--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93432</v>
+        <v>93438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93438</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93444</v>
+        <v>93457</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136457064</v>
       </c>
       <c r="B6" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93457</v>
+        <v>93458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136457064</v>
       </c>
       <c r="B6" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93458</v>
+        <v>93461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93461</v>
+        <v>93471</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136457064</v>
       </c>
       <c r="B6" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93471</v>
+        <v>93472</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93472</v>
+        <v>93477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136457064</v>
       </c>
       <c r="B6" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93477</v>
+        <v>93479</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 23960-2026 artfynd.xlsx
+++ b/artfynd/A 23960-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136457065</v>
       </c>
       <c r="B2" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136457066</v>
       </c>
       <c r="B3" t="n">
-        <v>93479</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136457062</v>
       </c>
       <c r="B4" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136457067</v>
       </c>
       <c r="B5" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>136457064</v>
       </c>
       <c r="B6" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>136457061</v>
       </c>
       <c r="B7" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
